--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487120_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487120_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3443</v>
+        <v>7.2898</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6463</v>
+        <v>4.4338</v>
       </c>
       <c r="F2" t="n">
-        <v>2.698</v>
+        <v>2.856</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8506</v>
+        <v>4.8653</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6732</v>
+        <v>-0.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1774</v>
+        <v>5.1052</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0652</v>
+        <v>4.6251</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1292</v>
+        <v>0.8487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9361</v>
+        <v>3.7765</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2147</v>
+        <v>0.2401</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.456</v>
+        <v>-1.0886</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2413</v>
+        <v>1.3288</v>
       </c>
       <c r="P2" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0881</v>
+        <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2355</v>
+        <v>0.3014</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5534</v>
+        <v>-0.1913</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6822</v>
+        <v>0.4927</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4906</v>
+        <v>5.7787</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5544</v>
+        <v>3.4823</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9363</v>
+        <v>2.2965</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8653</v>
+        <v>3.8506</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.24</v>
+        <v>2.6732</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1052</v>
+        <v>1.1774</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6251</v>
+        <v>5.0652</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8487</v>
+        <v>4.1292</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7765</v>
+        <v>0.9361</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2401</v>
+        <v>-1.2147</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0886</v>
+        <v>-1.456</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3288</v>
+        <v>0.2413</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1231</v>
+        <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4977</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0708</v>
+        <v>0.3894</v>
       </c>
       <c r="U3" t="n">
-        <v>0.573</v>
+        <v>1.2806</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3555</v>
+        <v>4.1615</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7799</v>
+        <v>2.3183</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5755</v>
+        <v>1.8432</v>
       </c>
       <c r="G4" t="n">
         <v>2.981</v>
@@ -766,13 +766,13 @@
         <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4904</v>
+        <v>0.3156</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3437</v>
+        <v>0.1947</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1468</v>
+        <v>0.1209</v>
       </c>
       <c r="V4" t="n">
         <v>0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7305</v>
+        <v>3.3839</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1246</v>
+        <v>1.8851</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6059</v>
+        <v>1.4988</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4565</v>
@@ -844,13 +844,13 @@
         <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.234</v>
+        <v>0.4194</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0708</v>
+        <v>-0.3103</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8368</v>
+        <v>0.7297</v>
       </c>
       <c r="V5" t="n">
         <v>2.4559</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4641</v>
+        <v>2.5365</v>
       </c>
       <c r="E6" t="n">
-        <v>3.164</v>
+        <v>3.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6999</v>
+        <v>-0.6464</v>
       </c>
       <c r="G6" t="n">
         <v>0.7072000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7919</v>
+        <v>0.8642</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2049</v>
+        <v>0.2238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5869</v>
+        <v>0.6405</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4298</v>
+        <v>-1.176</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.6833</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5462</v>
+        <v>-0.4927</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5933</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5433</v>
+        <v>-0.2895</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>0.0218</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3649</v>
+        <v>-0.3113</v>
       </c>
       <c r="V7" t="n">
         <v>0.2859</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.386</v>
+        <v>-3.8807</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.484</v>
+        <v>-4.9253</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0981</v>
+        <v>1.0445</v>
       </c>
       <c r="G8" t="n">
         <v>-4.7534</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9584</v>
+        <v>0.4637</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3239</v>
+        <v>-0.1173</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6345</v>
+        <v>0.581</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9421</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3099</v>
+        <v>-4.0511</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6565</v>
+        <v>-4.719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3466</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9728</v>
@@ -1156,13 +1156,13 @@
         <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0489</v>
+        <v>0.3077</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3834</v>
+        <v>0.3209</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3345</v>
+        <v>-0.0132</v>
       </c>
       <c r="V9" t="n">
         <v>-0.614</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7219</v>
+        <v>-4.5529</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5194</v>
+        <v>-3.8879</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2025</v>
+        <v>-0.665</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5163</v>
+        <v>-2.7878</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7927</v>
+        <v>-0.5329</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7236</v>
+        <v>-2.2549</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5676</v>
+        <v>-1.5067</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0621</v>
+        <v>-0.2122</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6297</v>
+        <v>-1.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9487</v>
+        <v>-1.2811</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8548</v>
+        <v>-0.3207</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0939</v>
+        <v>-0.9604</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2056</v>
+        <v>0.0998</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0132</v>
+        <v>-0.4511</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2188</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9733</v>
+        <v>-4.7358</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3886</v>
+        <v>-3.5601</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5847</v>
+        <v>-1.1757</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7878</v>
+        <v>-4.5163</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5329</v>
+        <v>-0.7927</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2549</v>
+        <v>-3.7236</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5067</v>
+        <v>-2.5676</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2122</v>
+        <v>0.0621</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2945</v>
+        <v>-2.6297</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2811</v>
+        <v>-1.9487</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3207</v>
+        <v>-0.8548</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9604</v>
+        <v>-1.0939</v>
       </c>
       <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.965</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3206</v>
+        <v>-0.2194</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9518</v>
+        <v>-0.0274</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6312</v>
+        <v>-0.192</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5641</v>
+        <v>4.753899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6629</v>
+        <v>-2.473200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>7.227100000000001</v>
+        <v>7.226999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.675999999999999</v>
@@ -1375,10 +1375,10 @@
         <v>-8.910300000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.417</v>
+        <v>-9.417000000000002</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5067999999999996</v>
+        <v>0.5067999999999997</v>
       </c>
       <c r="P12" t="n">
         <v>4.8252</v>
@@ -1390,13 +1390,13 @@
         <v>17.3707</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7431</v>
+        <v>3.932900000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1368</v>
+        <v>0.05320000000000006</v>
       </c>
       <c r="U12" t="n">
-        <v>3.8796</v>
+        <v>3.879799999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3282000000000002</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.6566</v>
+        <v>6.3468</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0818</v>
+        <v>5.2807</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5747</v>
+        <v>1.0661</v>
       </c>
       <c r="G13" t="n">
         <v>3.9144</v>
@@ -1468,13 +1468,13 @@
         <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6373</v>
+        <v>0.3275</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5619</v>
+        <v>-0.2393</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0754</v>
+        <v>0.5668</v>
       </c>
       <c r="V13" t="n">
         <v>3.0699</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3649</v>
+        <v>1.8185</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5191</v>
+        <v>-0.4081</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8458</v>
+        <v>2.2267</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2581</v>
+        <v>3.1954</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5816</v>
+        <v>1.8195</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8397</v>
+        <v>1.3759</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7554</v>
+        <v>2.3069</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7554</v>
+        <v>1.0452</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.2617</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0135</v>
+        <v>0.8885</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1738</v>
+        <v>0.7743</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8397</v>
+        <v>0.1142</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R14" t="n">
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9089</v>
+        <v>-0.6048</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4429</v>
+        <v>-0.5919</v>
       </c>
       <c r="U14" t="n">
-        <v>0.466</v>
+        <v>-0.0129</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1166</v>
+        <v>1.2992</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7085</v>
+        <v>2.1034</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8251</v>
+        <v>-0.8042</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1954</v>
+        <v>1.6922</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8195</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3759</v>
+        <v>1.7015</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3069</v>
+        <v>3.3599</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0452</v>
+        <v>1.4799</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2617</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8885</v>
+        <v>-1.6677</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7743</v>
+        <v>-1.4892</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1142</v>
+        <v>-0.1785</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3068</v>
+        <v>-0.586</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8923</v>
+        <v>-0.2915</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4145</v>
+        <v>-0.2945</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2968</v>
+        <v>0.423</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5026</v>
+        <v>-0.1819</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2057</v>
+        <v>0.6049</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6922</v>
+        <v>-0.2581</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.5816</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7015</v>
+        <v>-0.8397</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3599</v>
+        <v>0.7554</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4799</v>
+        <v>0.7554</v>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6677</v>
+        <v>-1.0135</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4892</v>
+        <v>-0.1738</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1785</v>
+        <v>-0.8397</v>
       </c>
       <c r="P16" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5884</v>
+        <v>-0.0331</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8923</v>
+        <v>-0.2581</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.696</v>
+        <v>0.225</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0035</v>
+        <v>0.2573</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3384</v>
+        <v>-0.1382</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3419</v>
+        <v>0.3955</v>
       </c>
       <c r="G17" t="n">
         <v>1.2843</v>
@@ -1780,13 +1780,13 @@
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6319</v>
+        <v>-0.3781</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5949</v>
+        <v>-0.3946</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.037</v>
+        <v>0.0165</v>
       </c>
       <c r="V17" t="n">
         <v>-1.228</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2822</v>
+        <v>-0.0621</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3274</v>
+        <v>-1.027</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0453</v>
+        <v>0.9649</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8090000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6313</v>
+        <v>-0.4111</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9518</v>
+        <v>-0.6514</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3205</v>
+        <v>0.2402</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5411</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0982</v>
+        <v>0.2567</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5571</v>
+        <v>-0.8459</v>
       </c>
       <c r="G19" t="n">
-        <v>0.843</v>
+        <v>-1.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5687</v>
+        <v>-1.035</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7258</v>
+        <v>0.0343</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3626</v>
+        <v>0.7078</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3169</v>
+        <v>0.7813</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9542</v>
+        <v>-0.0735</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-1.7085</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7481</v>
+        <v>-1.8163</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2285</v>
+        <v>0.1078</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.2811</v>
+        <v>0.965</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.0182</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9393</v>
+        <v>-0.5536</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5996</v>
+        <v>-0.4511</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3397</v>
+        <v>-0.1025</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3576</v>
+        <v>-2.3644</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.244</v>
+        <v>-3.6003</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1136</v>
+        <v>1.2359</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0007</v>
+        <v>0.843</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.035</v>
+        <v>2.5687</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0343</v>
+        <v>-1.7258</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7078</v>
+        <v>1.3626</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7813</v>
+        <v>3.3169</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0735</v>
+        <v>-1.9542</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7085</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8163</v>
+        <v>-0.7481</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1078</v>
+        <v>0.2285</v>
       </c>
       <c r="P20" t="n">
-        <v>0.965</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.0182</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.322</v>
+        <v>0.116</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9518</v>
+        <v>0.0975</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3702</v>
+        <v>0.0185</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6351</v>
+        <v>-2.4021</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4754</v>
+        <v>-0.9747</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1597</v>
+        <v>-1.4274</v>
       </c>
       <c r="G21" t="n">
         <v>-2.049</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3702</v>
+        <v>-0.1372</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>-0.3321</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4627</v>
+        <v>0.195</v>
       </c>
       <c r="V21" t="n">
         <v>0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3885</v>
+        <v>-2.9473</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.909</v>
+        <v>-3.7087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5205</v>
+        <v>0.7614</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5782</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9683</v>
+        <v>-0.5271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8923</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.076</v>
+        <v>0.1649</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7981</v>
+        <v>-5.344</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2296</v>
+        <v>-4.8291</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5685</v>
+        <v>-0.5149</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5584</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4098</v>
+        <v>0.0443</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.564200000000001</v>
+        <v>-3.564300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.226999999999999</v>
+        <v>-7.2272</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6629</v>
+        <v>3.662999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>3.675900000000002</v>
@@ -2329,10 +2329,10 @@
         <v>-2.7432</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.8797</v>
+        <v>-3.8798</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1367</v>
+        <v>1.1366</v>
       </c>
       <c r="V24" t="n">
         <v>0.3281000000000001</v>
